--- a/AAII_Financials/Quarterly/ZBAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZBAO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>ZBAO</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,147 +656,197 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>19600</v>
+        <v>6800</v>
       </c>
       <c r="E8" s="3">
-        <v>12700</v>
+        <v>6900</v>
       </c>
       <c r="F8" s="3">
-        <v>14900</v>
+        <v>5900</v>
       </c>
       <c r="G8" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K8" s="3">
         <v>8100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>11500</v>
+        <v>3800</v>
       </c>
       <c r="E9" s="3">
-        <v>8100</v>
+        <v>3800</v>
       </c>
       <c r="F9" s="3">
-        <v>8400</v>
+        <v>3800</v>
       </c>
       <c r="G9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J9" s="3">
         <v>4300</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3">
+        <v>4300</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>8100</v>
+        <v>3100</v>
       </c>
       <c r="E10" s="3">
-        <v>4600</v>
+        <v>3100</v>
       </c>
       <c r="F10" s="3">
-        <v>6500</v>
+        <v>2100</v>
       </c>
       <c r="G10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K10" s="3">
         <v>3900</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -808,37 +858,53 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="E12" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F12" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="G12" s="3">
+        <v>500</v>
+      </c>
+      <c r="H12" s="3">
+        <v>400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>400</v>
+      </c>
+      <c r="J12" s="3">
+        <v>300</v>
+      </c>
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -866,37 +932,61 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -924,8 +1014,20 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -934,66 +1036,94 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>25800</v>
+        <v>5600</v>
       </c>
       <c r="E17" s="3">
-        <v>11800</v>
+        <v>5600</v>
       </c>
       <c r="F17" s="3">
-        <v>13200</v>
+        <v>6500</v>
       </c>
       <c r="G17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K17" s="3">
         <v>7200</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-6200</v>
+        <v>1300</v>
       </c>
       <c r="E18" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="J18" s="3">
+        <v>500</v>
+      </c>
+      <c r="K18" s="3">
         <v>900</v>
       </c>
-      <c r="F18" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>900</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1005,153 +1135,217 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="H20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5600</v>
+        <v>1900</v>
       </c>
       <c r="E21" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>500</v>
+      </c>
+      <c r="K21" s="3">
         <v>1000</v>
       </c>
-      <c r="F21" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
-        <v>200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-5900</v>
+        <v>1900</v>
       </c>
       <c r="E23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J23" s="3">
+        <v>500</v>
+      </c>
+      <c r="K23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>900</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
+        <v>200</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1179,66 +1373,102 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6000</v>
+        <v>1500</v>
       </c>
       <c r="E26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>600</v>
+      </c>
+      <c r="K26" s="3">
         <v>1200</v>
       </c>
-      <c r="F26" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-6000</v>
+        <v>1500</v>
       </c>
       <c r="E27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J27" s="3">
+        <v>600</v>
+      </c>
+      <c r="K27" s="3">
         <v>1200</v>
       </c>
-      <c r="F27" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1266,8 +1496,20 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1295,8 +1537,20 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1324,8 +1578,20 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1353,66 +1619,102 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H32" s="3">
+        <v>200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-6000</v>
+        <v>1500</v>
       </c>
       <c r="E33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J33" s="3">
+        <v>600</v>
+      </c>
+      <c r="K33" s="3">
         <v>1200</v>
       </c>
-      <c r="F33" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1440,71 +1742,107 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-6000</v>
+        <v>1500</v>
       </c>
       <c r="E35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J35" s="3">
+        <v>600</v>
+      </c>
+      <c r="K35" s="3">
         <v>1200</v>
       </c>
-      <c r="F35" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1516,8 +1854,12 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1529,51 +1871,67 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>300</v>
+      </c>
+      <c r="F41" s="3">
+        <v>800</v>
+      </c>
+      <c r="G41" s="3">
+        <v>800</v>
+      </c>
+      <c r="H41" s="3">
         <v>1400</v>
       </c>
-      <c r="E41" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="I41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2100</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -1582,216 +1940,312 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>12000</v>
+        <v>18300</v>
       </c>
       <c r="E43" s="3">
-        <v>12600</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>18400</v>
+      </c>
+      <c r="F43" s="3">
+        <v>12100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>11800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I43" s="3">
+        <v>11300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>12300</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2300</v>
+        <v>2900</v>
       </c>
       <c r="E45" s="3">
-        <v>30300</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>2900</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2000</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>27400</v>
+      </c>
+      <c r="F46" s="3">
+        <v>31000</v>
+      </c>
+      <c r="G46" s="3">
+        <v>30100</v>
+      </c>
+      <c r="H46" s="3">
         <v>15700</v>
       </c>
-      <c r="E46" s="3">
-        <v>44900</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="I46" s="3">
+        <v>16600</v>
+      </c>
+      <c r="J46" s="3">
+        <v>47100</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>500</v>
+      </c>
+      <c r="G48" s="3">
+        <v>500</v>
+      </c>
+      <c r="H48" s="3">
         <v>600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
+        <v>600</v>
+      </c>
+      <c r="J48" s="3">
         <v>700</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E49" s="3">
         <v>400</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="F49" s="3">
+        <v>200</v>
+      </c>
+      <c r="G49" s="3">
+        <v>200</v>
+      </c>
+      <c r="H49" s="3">
+        <v>300</v>
+      </c>
+      <c r="I49" s="3">
+        <v>300</v>
+      </c>
+      <c r="J49" s="3">
+        <v>400</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1819,8 +2273,20 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1848,37 +2314,61 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="E52" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>700</v>
+      </c>
+      <c r="F52" s="3">
+        <v>900</v>
+      </c>
+      <c r="G52" s="3">
+        <v>900</v>
+      </c>
+      <c r="H52" s="3">
+        <v>900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>700</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1906,37 +2396,61 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>28900</v>
+      </c>
+      <c r="F54" s="3">
+        <v>33000</v>
+      </c>
+      <c r="G54" s="3">
+        <v>32100</v>
+      </c>
+      <c r="H54" s="3">
         <v>17700</v>
       </c>
-      <c r="E54" s="3">
-        <v>47300</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="I54" s="3">
+        <v>18600</v>
+      </c>
+      <c r="J54" s="3">
+        <v>49600</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1948,8 +2462,12 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1961,161 +2479,225 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>6100</v>
+      </c>
+      <c r="H57" s="3">
         <v>4300</v>
       </c>
-      <c r="E57" s="3">
-        <v>5700</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="I57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J57" s="3">
+        <v>6000</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3800</v>
+        <v>4900</v>
       </c>
       <c r="E58" s="3">
-        <v>3900</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>4900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>5700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>4200</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4900</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
-        <v>33300</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3300</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F60" s="3">
+        <v>30700</v>
+      </c>
+      <c r="G60" s="3">
+        <v>29800</v>
+      </c>
+      <c r="H60" s="3">
         <v>13000</v>
       </c>
-      <c r="E60" s="3">
-        <v>42900</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="I60" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J60" s="3">
+        <v>45000</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>300</v>
-      </c>
-      <c r="E62" s="3">
-        <v>500</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2135,8 +2717,20 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2164,8 +2758,20 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2193,8 +2799,20 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2222,37 +2840,61 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>30900</v>
+      </c>
+      <c r="G66" s="3">
+        <v>30000</v>
+      </c>
+      <c r="H66" s="3">
         <v>13300</v>
       </c>
-      <c r="E66" s="3">
-        <v>43300</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="I66" s="3">
+        <v>14100</v>
+      </c>
+      <c r="J66" s="3">
+        <v>45500</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2264,8 +2906,12 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2293,8 +2939,20 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2322,8 +2980,20 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2351,8 +3021,20 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2380,37 +3062,61 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="H72" s="3">
         <v>-19000</v>
       </c>
-      <c r="E72" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="I72" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-12400</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2438,8 +3144,20 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2467,8 +3185,20 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2496,37 +3226,61 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F76" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H76" s="3">
         <v>4300</v>
       </c>
-      <c r="E76" s="3">
-        <v>4000</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="I76" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>4200</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2554,71 +3308,107 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-6000</v>
+        <v>1500</v>
       </c>
       <c r="E81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J81" s="3">
+        <v>600</v>
+      </c>
+      <c r="K81" s="3">
         <v>1200</v>
       </c>
-      <c r="F81" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2630,8 +3420,12 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2642,25 +3436,37 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2688,8 +3494,20 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2717,8 +3535,20 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2746,8 +3576,20 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2775,8 +3617,20 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2804,37 +3658,61 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-200</v>
+        <v>-6200</v>
       </c>
       <c r="E89" s="3">
-        <v>28400</v>
+        <v>-6200</v>
       </c>
       <c r="F89" s="3">
-        <v>-100</v>
+        <v>6000</v>
       </c>
       <c r="G89" s="3">
+        <v>5900</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>14900</v>
+      </c>
+      <c r="K89" s="3">
         <v>2800</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2846,37 +3724,53 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2904,8 +3798,20 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2933,37 +3839,61 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2975,37 +3905,53 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3033,8 +3979,20 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3062,8 +4020,20 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3091,45 +4061,69 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-600</v>
+        <v>1500</v>
       </c>
       <c r="E100" s="3">
-        <v>-300</v>
+        <v>1500</v>
       </c>
       <c r="F100" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="G100" s="3">
+        <v>600</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
         <v>0</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -3149,33 +4143,57 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1100</v>
+        <v>-4700</v>
       </c>
       <c r="E102" s="3">
-        <v>30100</v>
+        <v>-4700</v>
       </c>
       <c r="F102" s="3">
-        <v>300</v>
+        <v>6700</v>
       </c>
       <c r="G102" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="J102" s="3">
+        <v>15800</v>
+      </c>
+      <c r="K102" s="3">
         <v>3800</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3" t="s">
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZBAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZBAO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>ZBAO</t>
   </si>
@@ -656,197 +656,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F8" s="3">
         <v>6800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>5900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>5800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>6700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>8100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>3800</v>
+        <v>7100</v>
       </c>
       <c r="E9" s="3">
-        <v>3800</v>
+        <v>7400</v>
       </c>
       <c r="F9" s="3">
         <v>3800</v>
       </c>
       <c r="G9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I9" s="3">
         <v>3700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>4300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>4300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F10" s="3">
         <v>3100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>3100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,16 +887,18 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E12" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F12" s="3">
         <v>500</v>
@@ -880,31 +907,37 @@
         <v>500</v>
       </c>
       <c r="H12" s="3">
+        <v>500</v>
+      </c>
+      <c r="I12" s="3">
+        <v>500</v>
+      </c>
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,16 +977,22 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>300</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -970,11 +1009,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -985,8 +1024,14 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1026,8 +1071,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,90 +1091,104 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F17" s="3">
         <v>5600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>6500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>6300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>7000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>7400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7200</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>300</v>
+      </c>
+      <c r="F18" s="3">
         <v>1300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-3500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,40 +1204,42 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1180,57 +1247,69 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>500</v>
+      </c>
+      <c r="F21" s="3">
         <v>1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1900</v>
       </c>
-      <c r="F21" s="3">
-        <v>-500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-500</v>
-      </c>
       <c r="H21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1242,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1250,11 +1329,11 @@
       <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>100</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1262,90 +1341,108 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,90 +1482,108 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>1500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>1500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1200</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,8 +1623,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1670,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1717,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,40 +1764,46 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>200</v>
+      </c>
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1672,49 +1811,61 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>1500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1200</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,95 +1905,113 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>1500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1200</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +2027,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,38 +2046,40 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1916,38 +2089,44 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>200</v>
       </c>
-      <c r="E42" s="3">
-        <v>200</v>
-      </c>
-      <c r="F42" s="3">
-        <v>200</v>
-      </c>
-      <c r="G42" s="3">
-        <v>200</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>200</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -1957,38 +2136,44 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>18300</v>
+        <v>18600</v>
       </c>
       <c r="E43" s="3">
-        <v>18400</v>
+        <v>19400</v>
       </c>
       <c r="F43" s="3">
+        <v>18600</v>
+      </c>
+      <c r="G43" s="3">
+        <v>18700</v>
+      </c>
+      <c r="H43" s="3">
         <v>12100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>11800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>10700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>11300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>12300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1998,8 +2183,14 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2024,11 +2215,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2039,38 +2230,44 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F45" s="3">
         <v>2900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2900</v>
       </c>
-      <c r="F45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3100</v>
-      </c>
       <c r="H45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>2000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2080,38 +2277,44 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>42400</v>
+      </c>
+      <c r="F46" s="3">
         <v>27200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>27400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>31000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>30100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>15700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>16600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>47100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,16 +2324,22 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>600</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -2147,11 +2356,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2162,16 +2371,22 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E48" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="F48" s="3">
         <v>500</v>
@@ -2180,20 +2395,20 @@
         <v>500</v>
       </c>
       <c r="H48" s="3">
+        <v>500</v>
+      </c>
+      <c r="I48" s="3">
+        <v>500</v>
+      </c>
+      <c r="J48" s="3">
         <v>600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>700</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2203,38 +2418,44 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>300</v>
+      </c>
+      <c r="F49" s="3">
         <v>400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>400</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2244,8 +2465,14 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2512,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,8 +2559,14 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2338,10 +2577,10 @@
         <v>700</v>
       </c>
       <c r="F52" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="G52" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="H52" s="3">
         <v>900</v>
@@ -2350,14 +2589,14 @@
         <v>900</v>
       </c>
       <c r="J52" s="3">
+        <v>900</v>
+      </c>
+      <c r="K52" s="3">
+        <v>900</v>
+      </c>
+      <c r="L52" s="3">
         <v>700</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2606,14 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,38 +2653,44 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>44900</v>
+      </c>
+      <c r="F54" s="3">
         <v>28700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>28900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>33000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>32100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>17700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>18600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>49600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,8 +2700,14 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2723,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,38 +2742,40 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F57" s="3">
         <v>7100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>6100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2524,38 +2785,44 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F58" s="3">
         <v>4900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>4900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2565,38 +2832,44 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>3400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2606,38 +2879,44 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>33500</v>
+      </c>
+      <c r="F60" s="3">
         <v>19400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>19500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>30700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>29800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>13000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>13700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>45000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,38 +2926,44 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>500</v>
+      </c>
+      <c r="F61" s="3">
         <v>100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>500</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2688,8 +2973,14 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2729,8 +3020,14 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +3067,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +3114,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,38 +3161,44 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>34500</v>
+      </c>
+      <c r="F66" s="3">
         <v>19900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>20100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>30900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>30000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>13300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>45500</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,8 +3208,14 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3231,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3274,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,8 +3321,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3033,8 +3368,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,38 +3415,44 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-18100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-18300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-21700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-21100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-19000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-20000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-12400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3115,8 +3462,14 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3509,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3556,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,38 +3603,44 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F76" s="3">
         <v>8800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3279,8 +3650,14 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,95 +3697,113 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>1500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1200</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,28 +3819,30 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -3453,11 +3850,11 @@
       <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
+        <v>100</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3465,8 +3862,14 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3909,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3956,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +4003,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +4050,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,49 +4097,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-6200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-6200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>6000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-14300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-15100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>14900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,22 +4167,24 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -3754,11 +4195,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3769,8 +4210,14 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4257,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,16 +4304,22 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -3869,31 +4328,37 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>1100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,8 +4374,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3935,11 +4402,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3950,8 +4417,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4464,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4511,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,49 +4558,61 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F100" s="3">
         <v>1500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>600</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-200</v>
       </c>
       <c r="J100" s="3">
         <v>-200</v>
       </c>
       <c r="K100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4125,11 +4622,11 @@
       <c r="E101" s="3">
         <v>0</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -4155,45 +4652,57 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>6700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>6500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-14500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-15300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>15800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>3800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZBAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZBAO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>ZBAO</t>
   </si>
@@ -656,222 +656,248 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F8" s="3">
         <v>10000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>10400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>6800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>6900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>6700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>8100</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F9" s="3">
         <v>7100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>7400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>3800</v>
       </c>
       <c r="H9" s="3">
         <v>3800</v>
       </c>
       <c r="I9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K9" s="3">
         <v>3700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>4300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>4300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F10" s="3">
         <v>2900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>3000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>3100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>3100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3900</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,22 +915,24 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>300</v>
+      </c>
+      <c r="F12" s="3">
         <v>400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>400</v>
-      </c>
-      <c r="F12" s="3">
-        <v>500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>500</v>
       </c>
       <c r="H12" s="3">
         <v>500</v>
@@ -913,31 +941,37 @@
         <v>500</v>
       </c>
       <c r="J12" s="3">
+        <v>500</v>
+      </c>
+      <c r="K12" s="3">
+        <v>500</v>
+      </c>
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,23 +1017,29 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1015,11 +1055,11 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1030,8 +1070,14 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1077,8 +1123,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1093,102 +1145,116 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F17" s="3">
         <v>9800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>10200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>6500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7200</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F18" s="3">
         <v>300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>1300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>900</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1206,46 +1272,48 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1253,55 +1321,67 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F21" s="3">
         <v>400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1312,10 +1392,10 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1327,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1335,11 +1415,11 @@
       <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
@@ -1347,102 +1427,120 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-4500</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-4500</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>1900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>900</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1488,102 +1586,120 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1200</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1200</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1629,8 +1745,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1676,8 +1798,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1723,8 +1851,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1770,46 +1904,52 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1817,55 +1957,67 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1200</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1911,107 +2063,125 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1200</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2029,8 +2199,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2048,44 +2220,46 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F41" s="3">
         <v>3900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2269,14 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2125,14 +2305,14 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>200</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -2142,44 +2322,50 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>18600</v>
+        <v>16000</v>
       </c>
       <c r="E43" s="3">
-        <v>19400</v>
+        <v>15800</v>
       </c>
       <c r="F43" s="3">
         <v>18600</v>
       </c>
       <c r="G43" s="3">
+        <v>19400</v>
+      </c>
+      <c r="H43" s="3">
+        <v>18600</v>
+      </c>
+      <c r="I43" s="3">
         <v>18700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>12100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>11800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>10700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>11300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>12300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,8 +2375,14 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2221,11 +2413,11 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2236,44 +2428,50 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F45" s="3">
         <v>3200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,44 +2481,50 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F46" s="3">
         <v>40800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>42400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>27200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>27400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>31000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>30100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>15700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>16600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>47100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2330,23 +2534,29 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F47" s="3">
         <v>600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>600</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,11 +2572,11 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2377,22 +2587,28 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>600</v>
+      </c>
+      <c r="F48" s="3">
         <v>800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
-      </c>
-      <c r="F48" s="3">
-        <v>500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>500</v>
       </c>
       <c r="H48" s="3">
         <v>500</v>
@@ -2401,20 +2617,20 @@
         <v>500</v>
       </c>
       <c r="J48" s="3">
+        <v>500</v>
+      </c>
+      <c r="K48" s="3">
+        <v>500</v>
+      </c>
+      <c r="L48" s="3">
         <v>600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>700</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2424,44 +2640,50 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>200</v>
+      </c>
+      <c r="F49" s="3">
         <v>300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>400</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,8 +2693,14 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2518,8 +2746,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2565,16 +2799,22 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F52" s="3">
         <v>700</v>
@@ -2583,10 +2823,10 @@
         <v>700</v>
       </c>
       <c r="H52" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="I52" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="J52" s="3">
         <v>900</v>
@@ -2595,14 +2835,14 @@
         <v>900</v>
       </c>
       <c r="L52" s="3">
+        <v>900</v>
+      </c>
+      <c r="M52" s="3">
+        <v>900</v>
+      </c>
+      <c r="N52" s="3">
         <v>700</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,8 +2852,14 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2659,44 +2905,50 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>23500</v>
+      </c>
+      <c r="F54" s="3">
         <v>43200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>44900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>28700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>33000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>32100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>17700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>49600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2706,8 +2958,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2725,8 +2983,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2744,44 +3004,46 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F57" s="3">
         <v>7600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>6100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>4600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>6000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,44 +3053,50 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F58" s="3">
         <v>6200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
-        <v>4900</v>
-      </c>
-      <c r="G58" s="3">
-        <v>4900</v>
-      </c>
       <c r="H58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J58" s="3">
         <v>5700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>4300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2838,44 +3106,50 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F59" s="3">
         <v>1900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1000</v>
-      </c>
       <c r="H59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J59" s="3">
         <v>2700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2885,44 +3159,50 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F60" s="3">
         <v>32200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>33500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>19400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>19500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>30700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>29800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>13000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>13700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>45000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2932,44 +3212,50 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>300</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -2979,8 +3265,14 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3026,8 +3318,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3073,8 +3371,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3120,8 +3424,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3167,44 +3477,50 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>20100</v>
+      </c>
+      <c r="F66" s="3">
         <v>33200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>34500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>19900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>20100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>30900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>30000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>14100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>45500</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3214,8 +3530,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3233,8 +3555,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3280,8 +3604,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3327,8 +3657,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3374,8 +3710,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3421,44 +3763,50 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-18200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-18900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-18100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-18300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-21700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-21100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-19000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-20000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-12400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3468,8 +3816,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3515,8 +3869,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3562,8 +3922,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3609,44 +3975,50 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F76" s="3">
         <v>10000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>8800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3656,8 +4028,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3703,107 +4081,125 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-4300</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1200</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3821,34 +4217,36 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
@@ -3856,11 +4254,11 @@
       <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
+        <v>100</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -3868,8 +4266,14 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3915,8 +4319,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3962,8 +4372,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4009,8 +4425,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4056,8 +4478,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4103,55 +4531,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="F89" s="3">
         <v>5100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>5300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-6200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>6000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>5900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-14300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-15100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>14900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4169,8 +4609,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4180,17 +4622,17 @@
       <c r="E91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -4201,11 +4643,11 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -4216,8 +4658,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4263,8 +4711,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4310,23 +4764,29 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -4334,31 +4794,37 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>1100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4376,8 +4842,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4408,11 +4876,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -4423,8 +4891,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4470,8 +4944,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4517,8 +4997,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4564,55 +5050,67 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-200</v>
       </c>
       <c r="L100" s="3">
         <v>-200</v>
       </c>
       <c r="M100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4628,11 +5126,11 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -4658,51 +5156,63 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F102" s="3">
         <v>6400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>6600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-4700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>6700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>6500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-14500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-15300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>15800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>3800</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ZBAO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZBAO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>ZBAO</t>
   </si>
@@ -656,248 +656,273 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F8" s="3">
         <v>9100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>9000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>10000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>10400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>6800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>6900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>5900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>5800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>3500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>6700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F9" s="3">
         <v>4200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>4100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>7100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>7400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I9" s="3">
-        <v>3800</v>
       </c>
       <c r="J9" s="3">
         <v>3800</v>
       </c>
       <c r="K9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M9" s="3">
         <v>3700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>4300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>4300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E10" s="3">
         <v>5000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G10" s="3">
         <v>4900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>3000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>3900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,8 +942,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,16 +956,16 @@
         <v>300</v>
       </c>
       <c r="F12" s="3">
+        <v>300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>300</v>
+      </c>
+      <c r="H12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>400</v>
-      </c>
-      <c r="H12" s="3">
-        <v>500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>500</v>
       </c>
       <c r="J12" s="3">
         <v>500</v>
@@ -947,31 +974,37 @@
         <v>500</v>
       </c>
       <c r="L12" s="3">
+        <v>500</v>
+      </c>
+      <c r="M12" s="3">
+        <v>500</v>
+      </c>
+      <c r="N12" s="3">
         <v>400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1023,29 +1056,35 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1061,11 +1100,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1076,16 +1115,22 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -1129,8 +1174,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1147,114 +1198,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>14100</v>
+      </c>
+      <c r="F17" s="3">
         <v>13100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>12900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>10200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>6300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>7000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7200</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-4000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>900</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1274,52 +1339,54 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1327,61 +1394,73 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-4700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-3300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1398,10 +1477,10 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1413,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1421,11 +1500,11 @@
       <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>100</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1433,114 +1512,132 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4500</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>900</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1592,114 +1689,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4200</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1200</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4200</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1200</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,8 +1866,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1804,8 +1925,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1857,8 +1984,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1910,52 +2043,58 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -1963,61 +2102,73 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4200</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1200</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2069,119 +2220,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4200</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1200</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2201,8 +2370,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2222,50 +2393,52 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2100</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,8 +2448,14 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2311,14 +2490,14 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>200</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -2328,50 +2507,56 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>17500</v>
+      </c>
+      <c r="F43" s="3">
         <v>16000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>15800</v>
-      </c>
-      <c r="F43" s="3">
-        <v>18600</v>
-      </c>
-      <c r="G43" s="3">
-        <v>19400</v>
       </c>
       <c r="H43" s="3">
         <v>18600</v>
       </c>
       <c r="I43" s="3">
+        <v>19400</v>
+      </c>
+      <c r="J43" s="3">
+        <v>18600</v>
+      </c>
+      <c r="K43" s="3">
         <v>18700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>12100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>11800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>10700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>11300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>12300</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2381,8 +2566,14 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2419,11 +2610,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2434,50 +2625,56 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F45" s="3">
         <v>2000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2000</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2487,50 +2684,56 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>27100</v>
+      </c>
+      <c r="F46" s="3">
         <v>20200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>19900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>40800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>42400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>27200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>27400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>31000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>30100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>15700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>16600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>47100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2540,29 +2743,35 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F47" s="3">
         <v>2100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>600</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2578,11 +2787,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2593,28 +2802,34 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>800</v>
+      </c>
+      <c r="F48" s="3">
         <v>600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
-      </c>
-      <c r="H48" s="3">
-        <v>500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>500</v>
       </c>
       <c r="J48" s="3">
         <v>500</v>
@@ -2623,20 +2838,20 @@
         <v>500</v>
       </c>
       <c r="L48" s="3">
+        <v>500</v>
+      </c>
+      <c r="M48" s="3">
+        <v>500</v>
+      </c>
+      <c r="N48" s="3">
         <v>600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>700</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,50 +2861,56 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F49" s="3">
         <v>200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>400</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2699,8 +2920,14 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2752,8 +2979,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2805,22 +3038,28 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>800</v>
-      </c>
-      <c r="F52" s="3">
-        <v>700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>700</v>
       </c>
       <c r="H52" s="3">
         <v>700</v>
@@ -2829,10 +3068,10 @@
         <v>700</v>
       </c>
       <c r="J52" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="K52" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="L52" s="3">
         <v>900</v>
@@ -2841,14 +3080,14 @@
         <v>900</v>
       </c>
       <c r="N52" s="3">
+        <v>900</v>
+      </c>
+      <c r="O52" s="3">
+        <v>900</v>
+      </c>
+      <c r="P52" s="3">
         <v>700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +3097,14 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2911,50 +3156,56 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>39800</v>
+      </c>
+      <c r="F54" s="3">
         <v>23800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>23500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>43200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>44900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>28700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>28900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>33000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>32100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>17700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>18600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>49600</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2964,8 +3215,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,8 +3242,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3006,50 +3265,52 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F57" s="3">
         <v>8200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>8100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>7100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>7100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>4600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,50 +3320,56 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F58" s="3">
         <v>3600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>6200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>6500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K58" s="3">
         <v>4000</v>
       </c>
-      <c r="I58" s="3">
-        <v>4000</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>5600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>4300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>4200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3112,50 +3379,56 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F59" s="3">
         <v>1600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="H59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3165,50 +3438,56 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>31300</v>
+      </c>
+      <c r="F60" s="3">
         <v>20100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>19900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>32200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>33500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>19400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>19500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>30700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>29800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>13000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>45000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3218,8 +3497,14 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3227,41 +3512,41 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>300</v>
+      </c>
+      <c r="H61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3271,8 +3556,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3324,8 +3615,14 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3377,8 +3674,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3430,8 +3733,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3483,50 +3792,56 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>32900</v>
+      </c>
+      <c r="F66" s="3">
         <v>20400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>20100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>33200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>34500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>19900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>20100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>30900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>30000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>13300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>45500</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3851,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3557,8 +3878,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3610,8 +3933,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3663,8 +3992,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3716,8 +4051,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3769,50 +4110,56 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-27100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-26700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-18200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-18900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-18100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-18300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-21700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-21100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-19000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-20000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-12400</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3822,8 +4169,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3875,8 +4228,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3928,8 +4287,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3981,50 +4346,56 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F76" s="3">
         <v>3400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>10000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4034,8 +4405,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4087,119 +4464,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4200</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1200</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4219,40 +4614,42 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -4260,11 +4657,11 @@
       <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>100</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4272,8 +4669,14 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4325,8 +4728,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4378,8 +4787,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4431,8 +4846,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4484,8 +4905,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4537,61 +4964,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-6600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-6500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-6200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-6200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>5900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-14300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-15100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>14900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4611,16 +5050,18 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -4628,17 +5069,17 @@
       <c r="G91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
@@ -4649,11 +5090,11 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4664,8 +5105,14 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4717,8 +5164,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4770,29 +5223,35 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
@@ -4800,31 +5259,37 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>1100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4844,8 +5309,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4882,11 +5349,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4897,8 +5364,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4950,8 +5423,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5003,8 +5482,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5056,61 +5541,73 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-200</v>
       </c>
       <c r="N100" s="3">
         <v>-200</v>
       </c>
       <c r="O100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5132,11 +5629,11 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -5162,57 +5659,69 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-8300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-8200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>6400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>6600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>6700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>6500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-14500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-15300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>15800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>3800</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
